--- a/Data/Output/faturas.xlsx
+++ b/Data/Output/faturas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://suzano-my.sharepoint.com/personal/julianobs_suzano_com_br/Documents/Area Dev/GitHub/UiPath/ExtracaoFaturasImgComIA/Data/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F6C175841C6F44F3B8203883EEA88F3378DC2D21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A73EAE20-388D-4E01-90DE-67CE53F56D0D}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F6C175841C6F44F3B8203883EEA88F3378DC2D21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A892708-37B9-43E9-81E2-D1E1FE32DA04}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,6 +89,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
